--- a/03_Outputs/Minero_Agroecologica/08_Educacion/educacion.xlsx
+++ b/03_Outputs/Minero_Agroecologica/08_Educacion/educacion.xlsx
@@ -3340,13 +3340,13 @@
         <v>2021</v>
       </c>
       <c r="F89" s="7">
-        <v>0.808399619674067</v>
+        <v>0.924418856993982</v>
       </c>
       <c r="G89" s="9">
-        <v>0.0340611041845194</v>
+        <v>0.0471531226376282</v>
       </c>
       <c r="H89" s="11">
-        <v>0.0537186135094694</v>
+        <v>0.0582136438740334</v>
       </c>
     </row>
     <row r="90">
